--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0001T0006Z000C1N32_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0001T0006Z000C1N32_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>48.88513577666636</v>
+        <v>7.943834563708283</v>
       </c>
       <c r="D2" t="n">
-        <v>48.91571565880086</v>
+        <v>7.948803794555141</v>
       </c>
       <c r="E2" t="n">
-        <v>12.77286404081966</v>
+        <v>2.075590406633194</v>
       </c>
       <c r="F2" t="n">
-        <v>12.77344538596711</v>
+        <v>2.075684875219656</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>26.44892807057937</v>
+        <v>4.297950811469147</v>
       </c>
       <c r="D3" t="n">
-        <v>26.42880540580565</v>
+        <v>4.294680878443418</v>
       </c>
       <c r="E3" t="n">
-        <v>12.77286404081966</v>
+        <v>2.075590406633194</v>
       </c>
       <c r="F3" t="n">
-        <v>12.77344538596711</v>
+        <v>2.075684875219656</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>22.95479576685054</v>
+        <v>3.730154312113214</v>
       </c>
       <c r="D4" t="n">
-        <v>22.84617401406879</v>
+        <v>3.712503277286179</v>
       </c>
       <c r="E4" t="n">
-        <v>12.77286404081966</v>
+        <v>2.075590406633194</v>
       </c>
       <c r="F4" t="n">
-        <v>12.77344538596711</v>
+        <v>2.075684875219656</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>40.39512855246834</v>
+        <v>6.564208389776106</v>
       </c>
       <c r="D5" t="n">
-        <v>40.53196887679901</v>
+        <v>6.58644494247984</v>
       </c>
       <c r="E5" t="n">
-        <v>12.77286404081966</v>
+        <v>2.075590406633194</v>
       </c>
       <c r="F5" t="n">
-        <v>12.77344538596711</v>
+        <v>2.075684875219656</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>24.86069838736178</v>
+        <v>4.03986348794629</v>
       </c>
       <c r="D6" t="n">
-        <v>25.00581166107413</v>
+        <v>4.063444394924546</v>
       </c>
       <c r="E6" t="n">
-        <v>12.77286404081966</v>
+        <v>2.075590406633194</v>
       </c>
       <c r="F6" t="n">
-        <v>12.77344538596711</v>
+        <v>2.075684875219656</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>37.87518006389433</v>
+        <v>6.154716760382829</v>
       </c>
       <c r="D7" t="n">
-        <v>37.99775077921187</v>
+        <v>6.174634501621929</v>
       </c>
       <c r="E7" t="n">
-        <v>12.77286404081966</v>
+        <v>2.075590406633194</v>
       </c>
       <c r="F7" t="n">
-        <v>12.77344538596711</v>
+        <v>2.075684875219656</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>60.72909636386517</v>
+        <v>9.86847815912809</v>
       </c>
       <c r="D8" t="n">
-        <v>60.66669793927227</v>
+        <v>9.858338415131744</v>
       </c>
       <c r="E8" t="n">
-        <v>12.77286404081966</v>
+        <v>2.075590406633194</v>
       </c>
       <c r="F8" t="n">
-        <v>12.77344538596711</v>
+        <v>2.075684875219656</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>49.82541229175477</v>
+        <v>8.09662949741015</v>
       </c>
       <c r="D9" t="n">
-        <v>49.92533449279156</v>
+        <v>8.112866855078629</v>
       </c>
       <c r="E9" t="n">
-        <v>12.77286404081966</v>
+        <v>2.075590406633194</v>
       </c>
       <c r="F9" t="n">
-        <v>12.77344538596711</v>
+        <v>2.075684875219656</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
